--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.3/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.3/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E3">
         <v>102</v>
       </c>
       <c r="G3">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>426</v>
